--- a/SGC-CKN/Excel/fa53dd90-0b12-4643-9131-c69846a185a3_Thanh_Hoá_P7-37_D800_11-04-2026.xlsx
+++ b/SGC-CKN/Excel/fa53dd90-0b12-4643-9131-c69846a185a3_Thanh_Hoá_P7-37_D800_11-04-2026.xlsx
@@ -35,7 +35,7 @@
     <t>Số hiệu cọc</t>
   </si>
   <si>
-    <t>P7-37</t>
+    <t>P7-38</t>
   </si>
   <si>
     <t>Tên Máy khoan</t>
